--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_antofagasta.xlsx
@@ -375,31 +375,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="C2">
-        <v>271615</v>
+        <v>89.70837709023345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Calama</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="C3">
-        <v>125268</v>
+        <v>84.67862481315396</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>21351</v>
+        <v>82.57338438333913</v>
       </c>
     </row>
     <row r="5">
@@ -429,52 +429,52 @@
         </is>
       </c>
       <c r="C5">
-        <v>11573</v>
+        <v>81.97917404547708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Sierra Gorda</t>
         </is>
       </c>
       <c r="C6">
-        <v>11105</v>
+        <v>76.99115044247787</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="C7">
-        <v>7931</v>
+        <v>70.96211365902293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sierra Gorda</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C8">
-        <v>1131</v>
+        <v>69.01909863392422</v>
       </c>
     </row>
   </sheetData>
@@ -530,7 +530,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -475,6 +475,3471 @@
       </c>
       <c r="C8">
         <v>69.01909863392422</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>45.52637198377109</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>44.92285321916148</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>44.78552387107197</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>43.08697838109603</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>41.72906739278421</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>41.43939930580152</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>40.53977473967557</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>39.48640600224311</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>39.15225282938287</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>37.38840297289948</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>36.48459099040495</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>35.26208304969367</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>33.57371068612345</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>32.53450764351927</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>32.18814195650634</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>30.85628870382234</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>30.08849557522124</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>28.08789078277728</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>26.54281443519112</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>26.12503398894226</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>25.83439687512086</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>25.6418726622215</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>25.63715821634374</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>25.55133694159463</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>24.45290900959506</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>23.88856158796338</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>23.54980513006435</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>22.19196732471069</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>22.11106480728574</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>20.96054402493447</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>20.09900607185675</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>19.79966071572825</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>19.31454196028187</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>17.17424670813475</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>17.04035874439462</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>16.54186521443158</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>16.26948865013329</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>16.09407097825317</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>16.00198342424028</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>15.90281221222639</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>15.77909270216963</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>15.18039482641253</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>14.90497544309203</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>14.43222475199219</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>14.3818065342729</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>14.36351259360109</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>14.02610350765884</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>14.00854255415572</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>13.99664642436327</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>13.71002049735081</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>13.67638743032555</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>13.49866709750384</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>13.3426151525699</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>13.20626276378489</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>13.00262237762238</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>12.92767585180987</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>12.89771513986761</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>12.55463286713287</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>12.50283241185534</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>12.43181979174046</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>12.17067815905025</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>12.04459164714436</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>12.02096762768294</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>11.9116680202653</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>11.84978922535484</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>11.83679251965715</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>11.58413442119719</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>11.50442477876106</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>11.43635125936011</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>11.36827773995916</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>11.20964791022931</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>11.1640571817563</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>11.00790091821482</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>11.00282322001779</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>10.9055658776961</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>10.82478390823168</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>10.66516360010876</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>10.19611619686395</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>10.05917159763314</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>9.910037543387405</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>9.900491949910554</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>9.873535212901729</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>9.86245808030454</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>9.850941209952838</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>9.757512472444599</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>9.742437794763376</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>9.331625026692292</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>9.094974792649211</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>8.917631041524848</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>8.784442128160972</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>8.777644339708148</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>8.76956860522774</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>8.705937957391447</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>8.616271620755926</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>8.396178984414279</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>8.138772564644658</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>8.132039385138485</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>7.596528596030091</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>7.407708570499268</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>7.345753347028405</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>6.838575183540288</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>6.822549647661755</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>6.712981662492932</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>6.603131381892444</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>6.479425360282788</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>6.262763784887679</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>6.256673072816571</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>5.692490648885998</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>5.624424452787419</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>5.513955071477195</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>5.313841512936536</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>5.090512684989429</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>5.059257602862254</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>4.857997010463378</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>4.836660432590665</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>4.748821716668178</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>4.488239825976615</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>4.424778761061947</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>4.356705241660994</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>4.299780406601969</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>4.282040242907641</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>4.227095177321422</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>3.954911367702065</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>3.877571829964651</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>3.865109217801142</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>3.820987155666855</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>3.758274610292548</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>3.753405025207351</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>3.624354210096982</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>3.610192150820267</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>3.594080338266385</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>3.54224264107985</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>3.471749489448604</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>3.22498413849361</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>3.182809596897972</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>3.124879142978691</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>2.995234853641933</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>2.975136360416519</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>2.92716133424098</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>2.891994506826077</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>2.859087814840027</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>2.769710278387759</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>2.668523030513981</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>2.624156366888925</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>2.567969988784468</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>2.522545998368531</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>2.518720217835262</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>2.490822985588689</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>2.451947248327339</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>2.314499659632403</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>2.309272508323298</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>2.178199707269475</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>2.150288123138802</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>2.084541903546429</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>1.985906470211403</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>1.974132062627638</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>1.964552637198377</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>1.902772943496925</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>1.900491138159299</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>1.844761573268361</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>1.827583764255862</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>1.783045056587657</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>1.756747184245945</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>1.741933291035983</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>1.665598975016015</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>1.634868122904015</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>1.633764465622873</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>1.48756818020826</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>1.484091394405296</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>1.445066232202309</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>1.430947132304598</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>1.40560626868083</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>1.387999145846679</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>1.381313310193384</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>1.317560388184458</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>1.219807738912675</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>1.20649156523596</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>1.203651345019792</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>1.181594568222475</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>1.167962253935105</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>1.114791178608934</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>1.04208740609096</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>1.02498398462524</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>0.9917121201388397</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>0.9609224855861627</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>0.8168822328114363</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>0.7916633007512723</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>0.790091821481956</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>0.7351159221261815</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>0.6265227984684998</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>0.6220211648759997</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>0.597786574036675</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>0.5491743048304134</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>0.525082801518701</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>0.5182349073751789</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>0.5170046045722595</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>0.5033846966986502</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>0.4911381592995943</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>0.4911381592995943</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>0.4533541120634696</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>0.4250194800595027</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>0.1857985297681558</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>0.1777203328217142</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>0.09609224855861627</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>0.08895076768379936</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>0.08500389601190055</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>0.07343673768092372</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>0.06807351940095303</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>0.06462557557153244</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>0.05996910066677508</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>0.04446861278256627</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>0.04305266020121454</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>0.04039098473220777</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>0.02322577721381311</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>0.01546969872761728</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>0.01416731600198342</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>0.002832411855343062</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
